--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Results" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,45 +505,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSTAGNN</t>
+          <t>STDMAE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PEMSD3</t>
+          <t>METR_LA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>IJCAI</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E2" t="n">
-        <v>15.57</v>
+        <v>3.4</v>
       </c>
       <c r="F2" t="n">
-        <v>27.21</v>
+        <v>9.59</v>
       </c>
       <c r="G2" t="n">
-        <v>14.68</v>
+        <v>7.07</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>failed: Traceback (most recent call last):
-  File "&lt;string&gt;", line 21, in &lt;module&gt;
-  File "/home/wangwenrui/opt/miniconda3/envs/autogen/lib/python3.10/asyncio/runners.py", line 44, in run
-    return loop.run_</t>
+          <t>exists</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -550,160 +548,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DSTAGNN</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PEMSD4</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ICML</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>31.46</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>failed: Traceback (most recent call last):
-  File "&lt;string&gt;", line 21, in &lt;module&gt;
-  File "/home/wangwenrui/opt/miniconda3/envs/autogen/lib/python3.10/asyncio/runners.py", line 44, in run
-    return loop.run_</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DSTAGNN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PEMSD7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ICML</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E4" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="F4" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>failed: Traceback (most recent call last):
-  File "&lt;string&gt;", line 21, in &lt;module&gt;
-  File "/home/wangwenrui/opt/miniconda3/envs/autogen/lib/python3.10/asyncio/runners.py", line 44, in run
-    return loop.run_</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DSTAGNN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PEMSD8</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ICML</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E5" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="F5" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>failed: Traceback (most recent call last):
-  File "&lt;string&gt;", line 21, in &lt;module&gt;
-  File "/home/wangwenrui/opt/miniconda3/envs/autogen/lib/python3.10/asyncio/runners.py", line 44, in run
-    return loop.run_</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>261.495612</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -764,44 +611,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSTAGNN</t>
+          <t>STDMAE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DSTAGNN: Dynamic Spatial-Temporal Aware Graph Neural Network for Traffic Flow Forecasting</t>
+          <t>STD-MAE: Spatial-Temporal Dual Masked Autoencoder for Traffic Forecasting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>IJCAI</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PEMSD3, PEMSD4, PEMSD7, PEMSD8</t>
+          <t>METR_LA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/SYLan2019/DSTAGNN</t>
+          <t>https://github.com/Jimmy-7664/STD-MAE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>failed: Traceback (most recent call last):
-  File "&lt;string&gt;", line 21, in &lt;module&gt;
-  File "/home/wangwenrui/opt/miniconda3/envs/autogen/lib/python3.10/asyncio/runners.py", line 44, in run
-    return loop.run_</t>
+          <t>exists</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>runtime_s</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>exp_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STDMAE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>METR_LA</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>261.495612</v>
+      </c>
+      <c r="I2" t="n">
+        <v>52740</v>
       </c>
     </row>
   </sheetData>
